--- a/data/out/variants/v6_no_econ_fuel_cost_lags/raw_v6_no_econ_fuel_cost_lags.xlsx
+++ b/data/out/variants/v6_no_econ_fuel_cost_lags/raw_v6_no_econ_fuel_cost_lags.xlsx
@@ -529,16 +529,16 @@
         <v>0.9466542332369257</v>
       </c>
       <c r="G2" t="n">
-        <v>47.05090468135142</v>
+        <v>47.05090468135145</v>
       </c>
       <c r="H2" t="n">
-        <v>13412.05366020366</v>
+        <v>13412.05366020365</v>
       </c>
       <c r="I2" t="n">
         <v>115.8104212072629</v>
       </c>
       <c r="J2" t="n">
-        <v>11.55270668712451</v>
+        <v>11.55270668712449</v>
       </c>
       <c r="K2" t="n">
         <v>48168</v>
@@ -550,7 +550,7 @@
         <v>9634</v>
       </c>
       <c r="N2" t="n">
-        <v>0.08525609970092773</v>
+        <v>0.05983495712280273</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -580,19 +580,19 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>0.9466517341778657</v>
+        <v>0.9466517213466302</v>
       </c>
       <c r="G3" t="n">
-        <v>47.06329885622897</v>
+        <v>47.06332443876622</v>
       </c>
       <c r="H3" t="n">
-        <v>13412.68196711992</v>
+        <v>13412.68519311572</v>
       </c>
       <c r="I3" t="n">
-        <v>115.8131338282491</v>
+        <v>115.8131477558387</v>
       </c>
       <c r="J3" t="n">
-        <v>11.55533923686645</v>
+        <v>11.55535091959345</v>
       </c>
       <c r="K3" t="n">
         <v>48168</v>
@@ -604,7 +604,7 @@
         <v>9634</v>
       </c>
       <c r="N3" t="n">
-        <v>0.06999707221984863</v>
+        <v>0.05017900466918945</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -634,19 +634,19 @@
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>0.9467875324300126</v>
+        <v>0.9467791464628216</v>
       </c>
       <c r="G4" t="n">
-        <v>46.44345455006018</v>
+        <v>46.49111775283669</v>
       </c>
       <c r="H4" t="n">
-        <v>13378.53992445617</v>
+        <v>13380.64830247346</v>
       </c>
       <c r="I4" t="n">
-        <v>115.6656384777094</v>
+        <v>115.6747522256843</v>
       </c>
       <c r="J4" t="n">
-        <v>11.3386623041116</v>
+        <v>11.36108896970591</v>
       </c>
       <c r="K4" t="n">
         <v>48168</v>
@@ -658,7 +658,7 @@
         <v>9634</v>
       </c>
       <c r="N4" t="n">
-        <v>2.888678073883057</v>
+        <v>2.749066352844238</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -692,19 +692,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.946541481604863</v>
+        <v>0.9465399220094726</v>
       </c>
       <c r="G5" t="n">
-        <v>47.48945801062642</v>
+        <v>47.49289691009101</v>
       </c>
       <c r="H5" t="n">
-        <v>13440.40138170546</v>
+        <v>13440.79349111418</v>
       </c>
       <c r="I5" t="n">
-        <v>115.9327450796601</v>
+        <v>115.9344361745646</v>
       </c>
       <c r="J5" t="n">
-        <v>11.62789706837747</v>
+        <v>11.62957712292101</v>
       </c>
       <c r="K5" t="n">
         <v>48168</v>
@@ -716,7 +716,7 @@
         <v>9634</v>
       </c>
       <c r="N5" t="n">
-        <v>40.21987414360046</v>
+        <v>32.00032138824463</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>-38.14572736748855</v>
+        <v>-38.14493542236941</v>
       </c>
     </row>
     <row r="6">
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.8414632613956305</v>
+        <v>0.8414632613956308</v>
       </c>
       <c r="G6" t="n">
-        <v>74.49491854489347</v>
+        <v>74.49491854489345</v>
       </c>
       <c r="H6" t="n">
-        <v>39858.89367227723</v>
+        <v>39858.89367227719</v>
       </c>
       <c r="I6" t="n">
-        <v>199.6469225214284</v>
+        <v>199.6469225214283</v>
       </c>
       <c r="J6" t="n">
-        <v>11.67003922183371</v>
+        <v>11.6700392218337</v>
       </c>
       <c r="K6" t="n">
         <v>48168</v>
@@ -776,7 +776,7 @@
         <v>9634</v>
       </c>
       <c r="N6" t="n">
-        <v>9.13952374458313</v>
+        <v>7.951109886169434</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>-72.45344687859908</v>
+        <v>-73.65134443835821</v>
       </c>
     </row>
     <row r="7">
@@ -808,23 +808,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>{'max_depth': 5, 'min_samples_split': 5, 'n_estimators': 500}</t>
+          <t>{'max_depth': 5, 'min_samples_split': 10, 'n_estimators': 500}</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.8171529743818824</v>
+        <v>0.8159635545828987</v>
       </c>
       <c r="G7" t="n">
-        <v>75.74314649869721</v>
+        <v>75.92297629686097</v>
       </c>
       <c r="H7" t="n">
-        <v>45970.92268052898</v>
+        <v>46269.96350675476</v>
       </c>
       <c r="I7" t="n">
-        <v>214.4083083290593</v>
+        <v>215.1045408789753</v>
       </c>
       <c r="J7" t="n">
-        <v>11.42770884362503</v>
+        <v>11.43628029675074</v>
       </c>
       <c r="K7" t="n">
         <v>48168</v>
@@ -836,7 +836,7 @@
         <v>9634</v>
       </c>
       <c r="N7" t="n">
-        <v>3876.013678789139</v>
+        <v>1922.35715675354</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-76.05088399982191</v>
+        <v>-76.14251849245382</v>
       </c>
     </row>
     <row r="8">
@@ -872,19 +872,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.7499516606381433</v>
+        <v>0.7460038253876595</v>
       </c>
       <c r="G8" t="n">
-        <v>87.55916506176975</v>
+        <v>88.14418244129619</v>
       </c>
       <c r="H8" t="n">
-        <v>62866.50185497791</v>
+        <v>63859.05630557366</v>
       </c>
       <c r="I8" t="n">
-        <v>250.7319322602885</v>
+        <v>252.7034948424213</v>
       </c>
       <c r="J8" t="n">
-        <v>12.65017972302226</v>
+        <v>12.67713574105626</v>
       </c>
       <c r="K8" t="n">
         <v>48168</v>
@@ -896,7 +896,7 @@
         <v>9634</v>
       </c>
       <c r="N8" t="n">
-        <v>1592.00726890564</v>
+        <v>568.4742803573608</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>-66.4006526741076</v>
+        <v>-68.02693589141771</v>
       </c>
     </row>
     <row r="9">
@@ -932,19 +932,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.2297922594752171</v>
+        <v>0.2303414987562742</v>
       </c>
       <c r="G9" t="n">
-        <v>213.4979634209127</v>
+        <v>214.7137991750686</v>
       </c>
       <c r="H9" t="n">
-        <v>193643.622957033</v>
+        <v>193505.5346483103</v>
       </c>
       <c r="I9" t="n">
-        <v>440.0495687499682</v>
+        <v>439.8926399115019</v>
       </c>
       <c r="J9" t="n">
-        <v>50.1140943548694</v>
+        <v>51.0177363438867</v>
       </c>
       <c r="K9" t="n">
         <v>48168</v>
@@ -956,7 +956,7 @@
         <v>9634</v>
       </c>
       <c r="N9" t="n">
-        <v>503.3628540039062</v>
+        <v>418.8646748065948</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>-197.8048931666694</v>
+        <v>-197.3358774663186</v>
       </c>
     </row>
     <row r="10">
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.7476207242635552</v>
+        <v>0.7470964997552659</v>
       </c>
       <c r="G10" t="n">
-        <v>132.6324704172721</v>
+        <v>133.5296482695216</v>
       </c>
       <c r="H10" t="n">
-        <v>63452.53980384354</v>
+        <v>63584.33896358561</v>
       </c>
       <c r="I10" t="n">
-        <v>251.8978757430152</v>
+        <v>252.1593523222678</v>
       </c>
       <c r="J10" t="n">
-        <v>34.15717275010522</v>
+        <v>34.08187737931478</v>
       </c>
       <c r="K10" t="n">
         <v>48168</v>
@@ -1016,7 +1016,7 @@
         <v>9634</v>
       </c>
       <c r="N10" t="n">
-        <v>7.21297550201416</v>
+        <v>6.388845205307007</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>-104.5420027361435</v>
+        <v>-104.7918229135463</v>
       </c>
     </row>
     <row r="11">
@@ -1048,23 +1048,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 384, 'learning_rate': 0.030355761006868417, 'max_depth': 3, 'subsample': 0.6909730888450774, 'colsample_bytree': 0.8101662845612609}</t>
+          <t>{'n_estimators': 514, 'learning_rate': 0.036436292466697766, 'max_depth': 3, 'subsample': 0.840369946632969, 'colsample_bytree': 0.8625392435526704}</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.8167294982392701</v>
+        <v>0.8130683491866131</v>
       </c>
       <c r="G11" t="n">
-        <v>77.59704553123825</v>
+        <v>78.72306895464517</v>
       </c>
       <c r="H11" t="n">
-        <v>46077.39194872335</v>
+        <v>46997.86850256734</v>
       </c>
       <c r="I11" t="n">
-        <v>214.6564509832475</v>
+        <v>216.7899178987975</v>
       </c>
       <c r="J11" t="n">
-        <v>11.97117271973907</v>
+        <v>12.23139219794703</v>
       </c>
       <c r="K11" t="n">
         <v>48168</v>
@@ -1076,7 +1076,7 @@
         <v>9634</v>
       </c>
       <c r="N11" t="n">
-        <v>207.7241413593292</v>
+        <v>191.9955909252167</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1106,23 +1106,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 346, 'learning_rate': 0.017862046325632416, 'num_leaves': 105, 'min_child_samples': 24}</t>
+          <t>{'n_estimators': 339, 'learning_rate': 0.015179061437193012, 'num_leaves': 111, 'min_child_samples': 21}</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.8094614906981861</v>
+        <v>0.8062838068014674</v>
       </c>
       <c r="G12" t="n">
-        <v>78.39047745129913</v>
+        <v>78.99149329042848</v>
       </c>
       <c r="H12" t="n">
-        <v>47904.69546423414</v>
+        <v>48703.62046848502</v>
       </c>
       <c r="I12" t="n">
-        <v>218.8714130813664</v>
+        <v>220.6889677090475</v>
       </c>
       <c r="J12" t="n">
-        <v>11.36869298418171</v>
+        <v>11.50704554408534</v>
       </c>
       <c r="K12" t="n">
         <v>48168</v>
@@ -1134,7 +1134,7 @@
         <v>9634</v>
       </c>
       <c r="N12" t="n">
-        <v>682.3712525367737</v>
+        <v>468.2241363525391</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1164,23 +1164,23 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>{'iterations': 585, 'learning_rate': 0.01623784466857658, 'depth': 4}</t>
+          <t>{'iterations': 904, 'learning_rate': 0.014737042834642606, 'depth': 4}</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.8115461575954558</v>
+        <v>0.8151164729920453</v>
       </c>
       <c r="G13" t="n">
-        <v>79.61806255242506</v>
+        <v>79.23506639915362</v>
       </c>
       <c r="H13" t="n">
-        <v>47380.57394557625</v>
+        <v>46482.93455282774</v>
       </c>
       <c r="I13" t="n">
-        <v>217.6707925872836</v>
+        <v>215.5990133391796</v>
       </c>
       <c r="J13" t="n">
-        <v>12.34549755424455</v>
+        <v>12.46680074133578</v>
       </c>
       <c r="K13" t="n">
         <v>48168</v>
@@ -1192,7 +1192,7 @@
         <v>9634</v>
       </c>
       <c r="N13" t="n">
-        <v>443.7327039241791</v>
+        <v>436.447957277298</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1222,23 +1222,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 100}</t>
+          <t>{'max_depth': 10, 'min_samples_split': 5, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.7830291831564375</v>
+        <v>0.7866350340103219</v>
       </c>
       <c r="G14" t="n">
-        <v>81.44445224446295</v>
+        <v>80.73379110656047</v>
       </c>
       <c r="H14" t="n">
-        <v>54550.23734363826</v>
+        <v>53643.66371882232</v>
       </c>
       <c r="I14" t="n">
-        <v>233.5599223831826</v>
+        <v>231.6110181291519</v>
       </c>
       <c r="J14" t="n">
-        <v>11.76307961740956</v>
+        <v>11.60054003418055</v>
       </c>
       <c r="K14" t="n">
         <v>48168</v>
@@ -1250,7 +1250,7 @@
         <v>9634</v>
       </c>
       <c r="N14" t="n">
-        <v>477.1248245239258</v>
+        <v>385.084086894989</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-70.41436575920285</v>
+        <v>-68.43938848346102</v>
       </c>
     </row>
     <row r="15">
@@ -1310,7 +1310,7 @@
         <v>9634</v>
       </c>
       <c r="N15" t="n">
-        <v>49.7326602935791</v>
+        <v>36.18001627922058</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1342,23 +1342,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>{'alpha': 0.01, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.001}</t>
+          <t>{'alpha': 0.0001, 'hidden_layer_sizes': (64,), 'learning_rate_init': 0.001}</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.9447628709223111</v>
+        <v>0.9431594478385283</v>
       </c>
       <c r="G16" t="n">
-        <v>49.74042058918155</v>
+        <v>50.61917139087414</v>
       </c>
       <c r="H16" t="n">
-        <v>13887.57504444319</v>
+        <v>14290.70349763827</v>
       </c>
       <c r="I16" t="n">
-        <v>117.8455558960252</v>
+        <v>119.5437304823564</v>
       </c>
       <c r="J16" t="n">
-        <v>11.50082501162444</v>
+        <v>12.04163030129807</v>
       </c>
       <c r="K16" t="n">
         <v>48168</v>
@@ -1370,7 +1370,7 @@
         <v>9634</v>
       </c>
       <c r="N16" t="n">
-        <v>2374.217186450958</v>
+        <v>1541.181994438171</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-38.81758032256019</v>
+        <v>-39.19917610109887</v>
       </c>
     </row>
   </sheetData>
